--- a/VerveStacks_NOR_grids_kan10/SuppXLS/Scen_TSParameters_ts_12t.xlsx
+++ b/VerveStacks_NOR_grids_kan10/SuppXLS/Scen_TSParameters_ts_12t.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NOR_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D0522B1D-512C-428F-AA01-9B767FABDA1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C69E479B-3DDC-499E-A9CF-91280FA0BE66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1837" yWindow="1837" windowWidth="21600" windowHeight="12683" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ev_charging_uc" sheetId="6" r:id="rId1"/>
@@ -609,10 +609,10 @@
     <t>day_night</t>
   </si>
   <si>
-    <t>WaP,FaP,SaP,SaD,RaD,FaD,RaP,WaD</t>
-  </si>
-  <si>
-    <t>RaN,SaN,WaN,WaP,FaP,SaP,RaP,FaN</t>
+    <t>WaD,RaP,SaD,RaD,FaD,FaP,SaP,WaP</t>
+  </si>
+  <si>
+    <t>FaP,SaP,RaP,FaN,WaP,SaN,WaN,RaN</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>RaN,SaN,WaN,WaP,FaP,SaP,RaP,FaN</v>
+        <v>FaP,SaP,RaP,FaN,WaP,SaN,WaN,RaN</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>WaP,FaP,SaP,SaD,RaD,FaD,RaP,WaD</v>
+        <v>WaD,RaP,SaD,RaD,FaD,FaP,SaP,WaP</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1335,7 +1335,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBE1D97D-B34E-4AE4-8CB0-7BAAE13AA554}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{673C03E1-14B2-442D-A306-5B65C164F84B}">
   <dimension ref="A9:G14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1419,7 +1419,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60C75559-36B7-4840-A7E9-6B4063D9F5B1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CBA05BD-7709-462F-8214-1C57A4E91A64}">
   <dimension ref="B9:O442"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -10409,7 +10409,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{613B4C15-7D99-402A-BB74-42C25FAB8B7B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98CE6B55-FACF-4CBC-BF60-2DEFB70A15B8}">
   <dimension ref="B9:BL66"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -16192,7 +16192,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3880191B-CB8F-4C70-9790-88A4165069AE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B0B5687-D269-4467-807D-C43268CF92D2}">
   <dimension ref="B9:E22"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -16390,7 +16390,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8D30D62-8329-47AC-A1FD-3F46CA07932C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{854D0097-7122-4819-A116-57F2548DDBE4}">
   <dimension ref="B9:D34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -16681,7 +16681,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{657094F3-6D38-4CF9-8E6B-2904F3B14222}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E3C340B-F58B-4983-9778-5D7B1B57F3EC}">
   <dimension ref="B9:D22"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -16840,7 +16840,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6968EEA8-34BE-4599-89F6-B3802E7E7AA9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6F8A05A-05FD-485F-B2B2-25BF75857804}">
   <dimension ref="B9:E126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -16886,7 +16886,7 @@
         <v>41</v>
       </c>
       <c r="D12">
-        <v>0.48293333333333327</v>
+        <v>0.48293333333333338</v>
       </c>
       <c r="E12" t="s">
         <v>196</v>
@@ -17068,7 +17068,7 @@
         <v>43</v>
       </c>
       <c r="D25">
-        <v>0.51190000000000002</v>
+        <v>0.51189999999999991</v>
       </c>
       <c r="E25" t="s">
         <v>196</v>
@@ -17082,7 +17082,7 @@
         <v>45</v>
       </c>
       <c r="D26">
-        <v>0.68703333333333327</v>
+        <v>0.68703333333333338</v>
       </c>
       <c r="E26" t="s">
         <v>196</v>
@@ -17110,7 +17110,7 @@
         <v>41</v>
       </c>
       <c r="D28">
-        <v>0.42379999999999995</v>
+        <v>0.42380000000000001</v>
       </c>
       <c r="E28" t="s">
         <v>196</v>
@@ -17278,7 +17278,7 @@
         <v>41</v>
       </c>
       <c r="D40">
-        <v>0.54619999999999991</v>
+        <v>0.54620000000000002</v>
       </c>
       <c r="E40" t="s">
         <v>196</v>
@@ -17320,7 +17320,7 @@
         <v>37</v>
       </c>
       <c r="D43">
-        <v>0.5126666666666666</v>
+        <v>0.51266666666666671</v>
       </c>
       <c r="E43" t="s">
         <v>196</v>
@@ -17348,7 +17348,7 @@
         <v>43</v>
       </c>
       <c r="D45">
-        <v>0.41166666666666668</v>
+        <v>0.41166666666666663</v>
       </c>
       <c r="E45" t="s">
         <v>196</v>
@@ -17404,7 +17404,7 @@
         <v>43</v>
       </c>
       <c r="D49">
-        <v>0.41726666666666662</v>
+        <v>0.41726666666666667</v>
       </c>
       <c r="E49" t="s">
         <v>196</v>
@@ -17418,7 +17418,7 @@
         <v>45</v>
       </c>
       <c r="D50">
-        <v>0.58139999999999992</v>
+        <v>0.58140000000000003</v>
       </c>
       <c r="E50" t="s">
         <v>196</v>
@@ -17488,7 +17488,7 @@
         <v>37</v>
       </c>
       <c r="D55">
-        <v>0.52036666666666664</v>
+        <v>0.52036666666666676</v>
       </c>
       <c r="E55" t="s">
         <v>196</v>
@@ -17544,7 +17544,7 @@
         <v>37</v>
       </c>
       <c r="D59">
-        <v>0.46543333333333331</v>
+        <v>0.46543333333333337</v>
       </c>
       <c r="E59" t="s">
         <v>196</v>
@@ -17642,7 +17642,7 @@
         <v>45</v>
       </c>
       <c r="D66">
-        <v>0.57210000000000005</v>
+        <v>0.57209999999999994</v>
       </c>
       <c r="E66" t="s">
         <v>196</v>
@@ -17684,7 +17684,7 @@
         <v>43</v>
       </c>
       <c r="D69">
-        <v>0.4041333333333334</v>
+        <v>0.40413333333333329</v>
       </c>
       <c r="E69" t="s">
         <v>196</v>
@@ -17698,7 +17698,7 @@
         <v>45</v>
       </c>
       <c r="D70">
-        <v>0.58056666666666668</v>
+        <v>0.58056666666666679</v>
       </c>
       <c r="E70" t="s">
         <v>196</v>
@@ -17754,7 +17754,7 @@
         <v>45</v>
       </c>
       <c r="D74">
-        <v>0.53883333333333328</v>
+        <v>0.53883333333333339</v>
       </c>
       <c r="E74" t="s">
         <v>196</v>
@@ -17768,7 +17768,7 @@
         <v>37</v>
       </c>
       <c r="D75">
-        <v>0.50383333333333324</v>
+        <v>0.50383333333333336</v>
       </c>
       <c r="E75" t="s">
         <v>196</v>
@@ -17824,7 +17824,7 @@
         <v>37</v>
       </c>
       <c r="D79">
-        <v>0.48076666666666662</v>
+        <v>0.48076666666666673</v>
       </c>
       <c r="E79" t="s">
         <v>196</v>
@@ -17894,7 +17894,7 @@
         <v>41</v>
       </c>
       <c r="D84">
-        <v>0.44943333333333335</v>
+        <v>0.4494333333333333</v>
       </c>
       <c r="E84" t="s">
         <v>196</v>
@@ -17922,7 +17922,7 @@
         <v>45</v>
       </c>
       <c r="D86">
-        <v>0.5806</v>
+        <v>0.58059999999999989</v>
       </c>
       <c r="E86" t="s">
         <v>196</v>
@@ -17964,7 +17964,7 @@
         <v>43</v>
       </c>
       <c r="D89">
-        <v>0.37610000000000005</v>
+        <v>0.37609999999999993</v>
       </c>
       <c r="E89" t="s">
         <v>196</v>
@@ -18034,7 +18034,7 @@
         <v>45</v>
       </c>
       <c r="D94">
-        <v>0.46300000000000002</v>
+        <v>0.46299999999999991</v>
       </c>
       <c r="E94" t="s">
         <v>196</v>
@@ -18118,7 +18118,7 @@
         <v>41</v>
       </c>
       <c r="D100">
-        <v>0.47150000000000003</v>
+        <v>0.47149999999999997</v>
       </c>
       <c r="E100" t="s">
         <v>196</v>
@@ -18146,7 +18146,7 @@
         <v>45</v>
       </c>
       <c r="D102">
-        <v>0.5379666666666667</v>
+        <v>0.53796666666666659</v>
       </c>
       <c r="E102" t="s">
         <v>196</v>
@@ -18174,7 +18174,7 @@
         <v>41</v>
       </c>
       <c r="D104">
-        <v>0.48726666666666674</v>
+        <v>0.48726666666666668</v>
       </c>
       <c r="E104" t="s">
         <v>196</v>
@@ -18300,7 +18300,7 @@
         <v>43</v>
       </c>
       <c r="D113">
-        <v>0.37453333333333333</v>
+        <v>0.37453333333333338</v>
       </c>
       <c r="E113" t="s">
         <v>196</v>
@@ -18328,7 +18328,7 @@
         <v>37</v>
       </c>
       <c r="D115">
-        <v>0.49659999999999993</v>
+        <v>0.49659999999999999</v>
       </c>
       <c r="E115" t="s">
         <v>196</v>
@@ -18370,7 +18370,7 @@
         <v>45</v>
       </c>
       <c r="D118">
-        <v>0.55986666666666662</v>
+        <v>0.55986666666666673</v>
       </c>
       <c r="E118" t="s">
         <v>196</v>
@@ -18384,7 +18384,7 @@
         <v>37</v>
       </c>
       <c r="D119">
-        <v>0.48433333333333328</v>
+        <v>0.48433333333333334</v>
       </c>
       <c r="E119" t="s">
         <v>196</v>
@@ -18454,7 +18454,7 @@
         <v>41</v>
       </c>
       <c r="D124">
-        <v>0.42926666666666669</v>
+        <v>0.42926666666666663</v>
       </c>
       <c r="E124" t="s">
         <v>196</v>
@@ -18482,7 +18482,7 @@
         <v>45</v>
       </c>
       <c r="D126">
-        <v>0.57599999999999996</v>
+        <v>0.57600000000000007</v>
       </c>
       <c r="E126" t="s">
         <v>196</v>
